--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY83"/>
+  <dimension ref="A1:AY90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96790349</v>
+        <v>109729419</v>
       </c>
       <c r="B2" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,43 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2059</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>mycel</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Getingfors by, 800 m SSO om, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>550712.7848898149</v>
+        <v>550796</v>
       </c>
       <c r="R2" t="n">
-        <v>6964503.400179885</v>
+        <v>6964537</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-09-08</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,40 +756,26 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>äldre tallskog, på morän med sand och småblock</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Magnus Andersson</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>109729419</v>
+        <v>109838387</v>
       </c>
       <c r="B3" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -845,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>550796.5433348599</v>
+        <v>550454</v>
       </c>
       <c r="R3" t="n">
-        <v>6964537.630448484</v>
+        <v>6964559</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,27 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>109729420</v>
+        <v>109838390</v>
       </c>
       <c r="B4" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6453</v>
+        <v>353</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>550640.0163002127</v>
+        <v>550495</v>
       </c>
       <c r="R4" t="n">
-        <v>6964469.341203836</v>
+        <v>6964512</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>109729422</v>
+        <v>109838396</v>
       </c>
       <c r="B5" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1045,21 +977,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1069,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>550640.0163002127</v>
+        <v>550479</v>
       </c>
       <c r="R5" t="n">
-        <v>6964469.341203836</v>
+        <v>6964446</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,27 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>109729421</v>
+        <v>113232562</v>
       </c>
       <c r="B6" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1157,34 +1074,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>229821</v>
+        <v>353</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>550640.0163002127</v>
+        <v>550807</v>
       </c>
       <c r="R6" t="n">
-        <v>6964469.341203836</v>
+        <v>6964786</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1211,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1241,27 +1148,26 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>109729411</v>
+        <v>109838401</v>
       </c>
       <c r="B7" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1269,21 +1175,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6453</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1293,10 +1199,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>550642.4600056082</v>
+        <v>550537</v>
       </c>
       <c r="R7" t="n">
-        <v>6964548.516266992</v>
+        <v>6964445</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1323,22 +1229,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1353,65 +1249,57 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>109729407</v>
+        <v>120722007</v>
       </c>
       <c r="B8" t="n">
-        <v>89323</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90674</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2013</v>
+        <v>1596</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kolticka</t>
+          <t>Jättemusseron</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Griseoporia carbonaria</t>
+          <t>Tricholoma colossus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>550766.8937254547</v>
+        <v>550546</v>
       </c>
       <c r="R8" t="n">
-        <v>6964559.128901197</v>
+        <v>6964601</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1438,22 +1326,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1462,74 +1340,66 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>Magnus Andersson</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Rasmus Viding</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>109729412</v>
+        <v>109729407</v>
       </c>
       <c r="B9" t="n">
-        <v>90653</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2013</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Griseoporia carbonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Berk. &amp; M.A.Curtis) Ginns</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>550642.4600056082</v>
+        <v>550767</v>
       </c>
       <c r="R9" t="n">
-        <v>6964548.516266992</v>
+        <v>6964559</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1559,29 +1429,25 @@
           <t>2023-05-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-05-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>Magnus Andersson</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1598,50 +1464,45 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>109838399</v>
+        <v>120721987</v>
       </c>
       <c r="B10" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91394</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6453</v>
+        <v>2051</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>550504.6786936504</v>
+        <v>550628</v>
       </c>
       <c r="R10" t="n">
-        <v>6964452.618678476</v>
+        <v>6964480</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,22 +1529,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1698,62 +1549,66 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>109838384</v>
+        <v>96790348</v>
       </c>
       <c r="B11" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Getingfors by, 700 m S om, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>550455.2143256323</v>
+        <v>550430</v>
       </c>
       <c r="R11" t="n">
-        <v>6964571.250221948</v>
+        <v>6964600</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1780,22 +1635,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1806,66 +1651,79 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>äldre renbetad sandtallskog med lav</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>109838400</v>
+        <v>96790349</v>
       </c>
       <c r="B12" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2059</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>mycel</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Getingfors by, 800 m SSO om, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>550536.3992460836</v>
+        <v>550713</v>
       </c>
       <c r="R12" t="n">
-        <v>6964445.33003449</v>
+        <v>6964504</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,22 +1750,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2021-09-08</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1918,66 +1766,70 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>äldre tallskog, på morän med sand och småblock</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Magnus Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Magnus Andersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>109838381</v>
+        <v>113232793</v>
       </c>
       <c r="B13" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>550561.9058657911</v>
+        <v>550574</v>
       </c>
       <c r="R13" t="n">
-        <v>6964484.605663798</v>
+        <v>6964592</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,22 +1856,12 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2034,62 +1876,61 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>109838398</v>
+        <v>113232795</v>
       </c>
       <c r="B14" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>2059</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>550504.6786936504</v>
+        <v>550554</v>
       </c>
       <c r="R14" t="n">
-        <v>6964452.618678476</v>
+        <v>6964553</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2116,22 +1957,12 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2146,62 +1977,61 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
-        </is>
-      </c>
-      <c r="AY14" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>109838382</v>
+        <v>113232798</v>
       </c>
       <c r="B15" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6453</v>
+        <v>2059</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>550535.5632458149</v>
+        <v>550698</v>
       </c>
       <c r="R15" t="n">
-        <v>6964588.953279356</v>
+        <v>6964720</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,22 +2058,12 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2258,62 +2078,61 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>109838380</v>
+        <v>113232800</v>
       </c>
       <c r="B16" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>550561.9058657911</v>
+        <v>550560</v>
       </c>
       <c r="R16" t="n">
-        <v>6964484.605663798</v>
+        <v>6964576</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,22 +2159,12 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,62 +2179,61 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>109838383</v>
+        <v>113232804</v>
       </c>
       <c r="B17" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>550535.5632458149</v>
+        <v>550531</v>
       </c>
       <c r="R17" t="n">
-        <v>6964588.953279356</v>
+        <v>6964417</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,22 +2260,12 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2482,62 +2280,61 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>109838393</v>
+        <v>113232825</v>
       </c>
       <c r="B18" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>550450.1096033145</v>
+        <v>550705</v>
       </c>
       <c r="R18" t="n">
-        <v>6964486.088355529</v>
+        <v>6964579</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2564,22 +2361,12 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,62 +2381,61 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
-        </is>
-      </c>
-      <c r="AY18" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>109838392</v>
+        <v>120721966</v>
       </c>
       <c r="B19" t="n">
-        <v>76909</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6437</v>
+        <v>2059</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blanksvart spiklav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Calicium denigratum</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Vain.) Tibell</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>550450.1096033145</v>
+        <v>550656</v>
       </c>
       <c r="R19" t="n">
-        <v>6964486.088355529</v>
+        <v>6964527</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2676,22 +2462,12 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2706,62 +2482,57 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>109838402</v>
+        <v>120721967</v>
       </c>
       <c r="B20" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6440</v>
+        <v>2059</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>550537.4700554342</v>
+        <v>550643</v>
       </c>
       <c r="R20" t="n">
-        <v>6964435.282601957</v>
+        <v>6964576</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2788,22 +2559,12 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2818,62 +2579,57 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>109838397</v>
+        <v>120721968</v>
       </c>
       <c r="B21" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>228912</v>
+        <v>2059</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>550504.6786936504</v>
+        <v>550576</v>
       </c>
       <c r="R21" t="n">
-        <v>6964452.618678476</v>
+        <v>6964408</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2900,22 +2656,12 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2930,62 +2676,57 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>109838387</v>
+        <v>120721969</v>
       </c>
       <c r="B22" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>353</v>
+        <v>2059</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>550454.0231139185</v>
+        <v>550567</v>
       </c>
       <c r="R22" t="n">
-        <v>6964559.338667458</v>
+        <v>6964436</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3012,22 +2753,12 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3042,27 +2773,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>109838401</v>
+        <v>113232513</v>
       </c>
       <c r="B23" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91962</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3070,34 +2796,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1312</v>
+        <v>2079</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Nordtagging</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Odonticium romellii</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(S.Lundell) Parmasto</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>550536.3992460836</v>
+        <v>550810</v>
       </c>
       <c r="R23" t="n">
-        <v>6964445.33003449</v>
+        <v>6964805</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3124,22 +2850,12 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3154,27 +2870,26 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>109838385</v>
+        <v>120721947</v>
       </c>
       <c r="B24" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93222</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3182,34 +2897,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>3100</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Talltaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Phellodon fuligineoalbus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(J.C.Schmidt) Baird</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>550455.2143256323</v>
+        <v>550507</v>
       </c>
       <c r="R24" t="n">
-        <v>6964571.250221948</v>
+        <v>6964494</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3236,22 +2951,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3266,27 +2971,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>109838386</v>
+        <v>120721933</v>
       </c>
       <c r="B25" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3294,34 +2994,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6446</v>
+        <v>3690</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>550455.2143256323</v>
+        <v>550656</v>
       </c>
       <c r="R25" t="n">
-        <v>6964571.250221948</v>
+        <v>6964570</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3348,22 +3048,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3378,27 +3068,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>109838390</v>
+        <v>120721934</v>
       </c>
       <c r="B26" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3406,34 +3091,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>3690</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>550494.6118481419</v>
+        <v>550552</v>
       </c>
       <c r="R26" t="n">
-        <v>6964511.474216321</v>
+        <v>6964467</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3460,22 +3145,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3490,27 +3165,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>109838391</v>
+        <v>120721935</v>
       </c>
       <c r="B27" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3518,34 +3188,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>229821</v>
+        <v>3690</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>550450.1096033145</v>
+        <v>550480</v>
       </c>
       <c r="R27" t="n">
-        <v>6964486.088355529</v>
+        <v>6964511</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3572,22 +3242,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3602,27 +3262,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>109838470</v>
+        <v>120721936</v>
       </c>
       <c r="B28" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3630,34 +3285,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>3690</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>550538.6000804405</v>
+        <v>550478</v>
       </c>
       <c r="R28" t="n">
-        <v>6964599.97831501</v>
+        <v>6964637</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3684,22 +3339,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-05-19</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3714,27 +3359,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>109838389</v>
+        <v>120721937</v>
       </c>
       <c r="B29" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3742,34 +3382,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>3690</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>550494.6118481419</v>
+        <v>550527</v>
       </c>
       <c r="R29" t="n">
-        <v>6964511.474216321</v>
+        <v>6964624</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3796,22 +3436,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3826,27 +3456,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>109838388</v>
+        <v>120721938</v>
       </c>
       <c r="B30" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>87325</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3854,34 +3479,34 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6453</v>
+        <v>3690</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaxspindling</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Cortinarius pinophilus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Soop</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Getingfors, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>550494.6118481419</v>
+        <v>550630</v>
       </c>
       <c r="R30" t="n">
-        <v>6964511.474216321</v>
+        <v>6964555</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3908,22 +3533,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-05-21</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3938,62 +3553,57 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Edith Bremer</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>113232832</v>
+        <v>120721991</v>
       </c>
       <c r="B31" t="n">
-        <v>89839</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>256703</v>
+        <v>4361</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tallfingersvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Ramaria eosanguinea</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>550412</v>
+        <v>550479</v>
       </c>
       <c r="R31" t="n">
-        <v>6964365</v>
+        <v>6964630</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4020,12 +3630,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4040,31 +3650,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>113232795</v>
+        <v>120721993</v>
       </c>
       <c r="B32" t="n">
-        <v>91621</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93189</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4072,34 +3673,34 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>2059</v>
+        <v>4361</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>550554</v>
+        <v>550573</v>
       </c>
       <c r="R32" t="n">
-        <v>6964553</v>
+        <v>6964598</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4126,12 +3727,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4146,31 +3747,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>113232804</v>
+        <v>113232836</v>
       </c>
       <c r="B33" t="n">
-        <v>91621</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4178,21 +3770,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4202,10 +3794,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>550531</v>
+        <v>550471</v>
       </c>
       <c r="R33" t="n">
-        <v>6964417</v>
+        <v>6964372</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4268,15 +3860,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>113232836</v>
+        <v>113232837</v>
       </c>
       <c r="B34" t="n">
-        <v>91599</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4308,10 +3895,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>550471</v>
+        <v>550385</v>
       </c>
       <c r="R34" t="n">
-        <v>6964372</v>
+        <v>6964401</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4374,15 +3961,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>113232793</v>
+        <v>120722062</v>
       </c>
       <c r="B35" t="n">
-        <v>91621</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4390,34 +3972,34 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>550574</v>
+        <v>550695</v>
       </c>
       <c r="R35" t="n">
-        <v>6964592</v>
+        <v>6964555</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4444,12 +4026,12 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4464,66 +4046,57 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
-        </is>
-      </c>
-      <c r="AY35" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>113232811</v>
+        <v>120722063</v>
       </c>
       <c r="B36" t="n">
-        <v>89025</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6276</v>
+        <v>4362</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>550652</v>
+        <v>550642</v>
       </c>
       <c r="R36" t="n">
-        <v>6964521</v>
+        <v>6964564</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4550,12 +4123,12 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4570,66 +4143,57 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
-        </is>
-      </c>
-      <c r="AY36" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>113232831</v>
+        <v>120722064</v>
       </c>
       <c r="B37" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>550412</v>
+        <v>550581</v>
       </c>
       <c r="R37" t="n">
-        <v>6964365</v>
+        <v>6964481</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4656,12 +4220,12 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4676,66 +4240,57 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
-        </is>
-      </c>
-      <c r="AY37" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>113232794</v>
+        <v>120722065</v>
       </c>
       <c r="B38" t="n">
-        <v>91617</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>4366</v>
+        <v>4362</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>550554</v>
+        <v>550575</v>
       </c>
       <c r="R38" t="n">
-        <v>6964553</v>
+        <v>6964453</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4762,12 +4317,12 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4782,31 +4337,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
-        </is>
-      </c>
-      <c r="AY38" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>113232825</v>
+        <v>120722066</v>
       </c>
       <c r="B39" t="n">
-        <v>91621</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4814,34 +4360,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>550705</v>
+        <v>550570</v>
       </c>
       <c r="R39" t="n">
-        <v>6964579</v>
+        <v>6964404</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4868,12 +4414,12 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4888,31 +4434,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
-        </is>
-      </c>
-      <c r="AY39" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>113232800</v>
+        <v>120722068</v>
       </c>
       <c r="B40" t="n">
-        <v>91621</v>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4920,34 +4457,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2059</v>
+        <v>4362</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
+          <t>Getingsfors, Jmt</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>550560</v>
+        <v>550555</v>
       </c>
       <c r="R40" t="n">
-        <v>6964576</v>
+        <v>6964459</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4974,12 +4511,12 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2023-08-28</t>
+          <t>2024-09-10</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4994,31 +4531,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Johan Staaf</t>
+          <t>Erica Hästdahl</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Pontus Wallén</t>
-        </is>
-      </c>
-      <c r="AY40" t="inlineStr">
-        <is>
-          <t>LstZ inventering av skogliga värdetrakter 2023</t>
-        </is>
-      </c>
+          <t>Erica Hästdahl</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>120722065</v>
+        <v>120722069</v>
       </c>
       <c r="B41" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5050,10 +4578,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>550575</v>
+        <v>550511</v>
       </c>
       <c r="R41" t="n">
-        <v>6964453</v>
+        <v>6964578</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5112,15 +4640,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>120721937</v>
+        <v>120722070</v>
       </c>
       <c r="B42" t="n">
-        <v>86233</v>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5128,21 +4651,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5152,10 +4675,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>550527</v>
+        <v>550497</v>
       </c>
       <c r="R42" t="n">
-        <v>6964624</v>
+        <v>6964626</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5214,37 +4737,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>120721943</v>
+        <v>120722071</v>
       </c>
       <c r="B43" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6286</v>
+        <v>4362</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Torrmusseron</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tricholoma sudum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5254,10 +4772,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>550585</v>
+        <v>550547</v>
       </c>
       <c r="R43" t="n">
-        <v>6964561</v>
+        <v>6964617</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5316,15 +4834,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>120721993</v>
+        <v>120722072</v>
       </c>
       <c r="B44" t="n">
-        <v>91950</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5332,21 +4845,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>4361</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5356,10 +4869,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>550573</v>
+        <v>550577</v>
       </c>
       <c r="R44" t="n">
-        <v>6964598</v>
+        <v>6964597</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5418,15 +4931,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>120721935</v>
+        <v>120722075</v>
       </c>
       <c r="B45" t="n">
-        <v>86233</v>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5434,21 +4942,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>3690</v>
+        <v>4362</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5458,10 +4966,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>550480</v>
+        <v>550613</v>
       </c>
       <c r="R45" t="n">
-        <v>6964511</v>
+        <v>6964642</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5520,15 +5028,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>120722066</v>
+        <v>120722076</v>
       </c>
       <c r="B46" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5560,10 +5063,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>550570</v>
+        <v>550618</v>
       </c>
       <c r="R46" t="n">
-        <v>6964404</v>
+        <v>6964650</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5622,15 +5125,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>120722070</v>
+        <v>120722077</v>
       </c>
       <c r="B47" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5662,10 +5160,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>550497</v>
+        <v>550637</v>
       </c>
       <c r="R47" t="n">
-        <v>6964626</v>
+        <v>6964515</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5724,50 +5222,45 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>120722007</v>
+        <v>109729412</v>
       </c>
       <c r="B48" t="n">
-        <v>89343</v>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>1596</v>
+        <v>4364</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Jättemusseron</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tricholoma colossus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Fr.) Quél.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>550546</v>
+        <v>550642</v>
       </c>
       <c r="R48" t="n">
-        <v>6964601</v>
+        <v>6964548</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5794,12 +5287,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5814,49 +5307,44 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>120722012</v>
+        <v>120722016</v>
       </c>
       <c r="B49" t="n">
-        <v>90213</v>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6039941</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5866,10 +5354,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>550640</v>
+        <v>550487</v>
       </c>
       <c r="R49" t="n">
-        <v>6964488</v>
+        <v>6964560</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5928,15 +5416,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>120722077</v>
+        <v>120722019</v>
       </c>
       <c r="B50" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5944,21 +5427,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5968,10 +5451,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>550637</v>
+        <v>550730</v>
       </c>
       <c r="R50" t="n">
-        <v>6964515</v>
+        <v>6964500</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6030,15 +5513,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>120721934</v>
+        <v>113232531</v>
       </c>
       <c r="B51" t="n">
-        <v>86233</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6046,34 +5524,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3690</v>
+        <v>4366</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>550552</v>
+        <v>550830</v>
       </c>
       <c r="R51" t="n">
-        <v>6964467</v>
+        <v>6964725</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6100,12 +5578,12 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6120,27 +5598,26 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY51" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>120721962</v>
+        <v>113232794</v>
       </c>
       <c r="B52" t="n">
-        <v>91986</v>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6148,34 +5625,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>550513</v>
+        <v>550554</v>
       </c>
       <c r="R52" t="n">
-        <v>6964563</v>
+        <v>6964553</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6202,12 +5679,12 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6222,31 +5699,30 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY52" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>120721971</v>
+        <v>113232831</v>
       </c>
       <c r="B53" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
@@ -6270,14 +5746,14 @@
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>550496</v>
+        <v>550412</v>
       </c>
       <c r="R53" t="n">
-        <v>6964599</v>
+        <v>6964365</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6304,12 +5780,12 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6324,27 +5800,26 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY53" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>120722068</v>
+        <v>120721971</v>
       </c>
       <c r="B54" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6352,21 +5827,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6376,10 +5851,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>550555</v>
+        <v>550496</v>
       </c>
       <c r="R54" t="n">
-        <v>6964459</v>
+        <v>6964599</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6438,15 +5913,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>120722062</v>
+        <v>120721972</v>
       </c>
       <c r="B55" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6454,21 +5924,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4362</v>
+        <v>4366</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6478,10 +5948,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>550695</v>
+        <v>550534</v>
       </c>
       <c r="R55" t="n">
-        <v>6964555</v>
+        <v>6964619</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6540,15 +6010,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>120721958</v>
+        <v>120721973</v>
       </c>
       <c r="B56" t="n">
-        <v>91986</v>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6556,21 +6021,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5449</v>
+        <v>4366</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6580,10 +6045,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>550509</v>
+        <v>550571</v>
       </c>
       <c r="R56" t="n">
-        <v>6964539</v>
+        <v>6964588</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6642,15 +6107,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>120721960</v>
+        <v>120721948</v>
       </c>
       <c r="B57" t="n">
-        <v>91986</v>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6658,21 +6118,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5449</v>
+        <v>4745</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6682,10 +6142,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>550561</v>
+        <v>550526</v>
       </c>
       <c r="R57" t="n">
-        <v>6964551</v>
+        <v>6964481</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6744,37 +6204,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>120721973</v>
+        <v>120721949</v>
       </c>
       <c r="B58" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4366</v>
+        <v>4745</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6784,10 +6239,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>550571</v>
+        <v>550505</v>
       </c>
       <c r="R58" t="n">
-        <v>6964588</v>
+        <v>6964580</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6846,15 +6301,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>120721967</v>
+        <v>120721951</v>
       </c>
       <c r="B59" t="n">
-        <v>91974</v>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92841</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6862,21 +6312,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>2059</v>
+        <v>4745</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Tallriska</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Lactarius musteus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6886,10 +6336,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>550643</v>
+        <v>550615</v>
       </c>
       <c r="R59" t="n">
-        <v>6964576</v>
+        <v>6964651</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6948,50 +6398,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>120721957</v>
+        <v>113232489</v>
       </c>
       <c r="B60" t="n">
-        <v>91986</v>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängsselet, Jmt</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>550523</v>
+        <v>550811</v>
       </c>
       <c r="R60" t="n">
-        <v>6964500</v>
+        <v>6964810</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7018,12 +6463,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7038,62 +6483,61 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY60" t="inlineStr"/>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>120721961</v>
+        <v>113232811</v>
       </c>
       <c r="B61" t="n">
-        <v>91986</v>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>5449</v>
+        <v>6276</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>550542</v>
+        <v>550652</v>
       </c>
       <c r="R61" t="n">
-        <v>6964554</v>
+        <v>6964521</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7120,12 +6564,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-08-28</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7140,49 +6584,48 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Johan Staaf</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
-        </is>
-      </c>
-      <c r="AY61" t="inlineStr"/>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>120722063</v>
+        <v>120722010</v>
       </c>
       <c r="B62" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7192,10 +6635,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>550642</v>
+        <v>550507</v>
       </c>
       <c r="R62" t="n">
-        <v>6964564</v>
+        <v>6964571</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7254,37 +6697,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>120722064</v>
+        <v>120722011</v>
       </c>
       <c r="B63" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90691</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4362</v>
+        <v>6276</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7294,10 +6732,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>550581</v>
+        <v>550470</v>
       </c>
       <c r="R63" t="n">
-        <v>6964481</v>
+        <v>6964613</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7356,37 +6794,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>120721947</v>
+        <v>120721943</v>
       </c>
       <c r="B64" t="n">
-        <v>91983</v>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>90710</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>3100</v>
+        <v>6286</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Talltaggsvamp</t>
+          <t>Torrmusseron</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon fuligineoalbus</t>
+          <t>Tricholoma sudum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(J.C.Schmidt) Baird</t>
+          <t>(Fr.) Quél.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7396,10 +6829,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>550507</v>
+        <v>550585</v>
       </c>
       <c r="R64" t="n">
-        <v>6964494</v>
+        <v>6964561</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7458,50 +6891,45 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>120721938</v>
+        <v>109838400</v>
       </c>
       <c r="B65" t="n">
-        <v>86233</v>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>3690</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>550630</v>
+        <v>550537</v>
       </c>
       <c r="R65" t="n">
-        <v>6964555</v>
+        <v>6964445</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7528,12 +6956,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7548,62 +6976,57 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>120721972</v>
+        <v>109838392</v>
       </c>
       <c r="B66" t="n">
-        <v>91970</v>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78730</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4366</v>
+        <v>6437</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Blanksvart spiklav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Calicium denigratum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Vain.) Tibell</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>550534</v>
+        <v>550450</v>
       </c>
       <c r="R66" t="n">
-        <v>6964619</v>
+        <v>6964486</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7630,12 +7053,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7650,27 +7073,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>120721951</v>
+        <v>109838402</v>
       </c>
       <c r="B67" t="n">
-        <v>91584</v>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7678,34 +7096,34 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4745</v>
+        <v>6440</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>550615</v>
+        <v>550538</v>
       </c>
       <c r="R67" t="n">
-        <v>6964651</v>
+        <v>6964435</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7732,12 +7150,12 @@
       </c>
       <c r="Y67" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7752,62 +7170,57 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>120722019</v>
+        <v>109838386</v>
       </c>
       <c r="B68" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>550730</v>
+        <v>550455</v>
       </c>
       <c r="R68" t="n">
-        <v>6964500</v>
+        <v>6964571</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7834,12 +7247,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7854,27 +7267,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>120721959</v>
+        <v>109729411</v>
       </c>
       <c r="B69" t="n">
-        <v>91986</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7882,34 +7290,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>550521</v>
+        <v>550642</v>
       </c>
       <c r="R69" t="n">
-        <v>6964527</v>
+        <v>6964548</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7936,12 +7344,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7956,27 +7364,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>120721966</v>
+        <v>109729420</v>
       </c>
       <c r="B70" t="n">
-        <v>91974</v>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7984,34 +7387,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>550656</v>
+        <v>550640</v>
       </c>
       <c r="R70" t="n">
-        <v>6964527</v>
+        <v>6964470</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8038,12 +7441,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8058,27 +7461,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>120721969</v>
+        <v>109838381</v>
       </c>
       <c r="B71" t="n">
-        <v>91974</v>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8086,34 +7484,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>550567</v>
+        <v>550562</v>
       </c>
       <c r="R71" t="n">
-        <v>6964436</v>
+        <v>6964484</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8140,12 +7538,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8160,27 +7558,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>120721968</v>
+        <v>109838382</v>
       </c>
       <c r="B72" t="n">
-        <v>91974</v>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8188,34 +7581,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>2059</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>550576</v>
+        <v>550536</v>
       </c>
       <c r="R72" t="n">
-        <v>6964408</v>
+        <v>6964589</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8242,12 +7635,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8262,27 +7655,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>120722071</v>
+        <v>109838384</v>
       </c>
       <c r="B73" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8290,34 +7678,34 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>550547</v>
+        <v>550455</v>
       </c>
       <c r="R73" t="n">
-        <v>6964617</v>
+        <v>6964571</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8344,12 +7732,12 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8364,27 +7752,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>120722069</v>
+        <v>109838388</v>
       </c>
       <c r="B74" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8392,34 +7775,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>550511</v>
+        <v>550495</v>
       </c>
       <c r="R74" t="n">
-        <v>6964578</v>
+        <v>6964512</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8446,12 +7829,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8466,27 +7849,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>120721933</v>
+        <v>109838395</v>
       </c>
       <c r="B75" t="n">
-        <v>86233</v>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8494,34 +7872,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>3690</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vaxspindling</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius pinophilus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Soop</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>550656</v>
+        <v>550479</v>
       </c>
       <c r="R75" t="n">
-        <v>6964570</v>
+        <v>6964446</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8548,12 +7926,12 @@
       </c>
       <c r="Y75" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8568,27 +7946,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>120722072</v>
+        <v>109838399</v>
       </c>
       <c r="B76" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8596,34 +7969,34 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4362</v>
+        <v>6453</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>550577</v>
+        <v>550504</v>
       </c>
       <c r="R76" t="n">
-        <v>6964597</v>
+        <v>6964453</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8650,12 +8023,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8670,27 +8043,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>120722076</v>
+        <v>109729422</v>
       </c>
       <c r="B77" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8698,34 +8066,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>550618</v>
+        <v>550640</v>
       </c>
       <c r="R77" t="n">
-        <v>6964650</v>
+        <v>6964470</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8752,12 +8120,12 @@
       </c>
       <c r="Y77" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-19</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8772,62 +8140,57 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Rasmus Viding</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>120722016</v>
+        <v>109838380</v>
       </c>
       <c r="B78" t="n">
-        <v>91958</v>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>550487</v>
+        <v>550562</v>
       </c>
       <c r="R78" t="n">
-        <v>6964560</v>
+        <v>6964484</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8854,12 +8217,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8874,27 +8237,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>120721948</v>
+        <v>109838383</v>
       </c>
       <c r="B79" t="n">
-        <v>91584</v>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8902,34 +8260,34 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>4745</v>
+        <v>228912</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>550526</v>
+        <v>550536</v>
       </c>
       <c r="R79" t="n">
-        <v>6964481</v>
+        <v>6964589</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8956,12 +8314,12 @@
       </c>
       <c r="Y79" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8976,27 +8334,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>120721949</v>
+        <v>109838385</v>
       </c>
       <c r="B80" t="n">
-        <v>91584</v>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9004,34 +8357,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4745</v>
+        <v>228912</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallriska</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lactarius musteus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>550505</v>
+        <v>550455</v>
       </c>
       <c r="R80" t="n">
-        <v>6964580</v>
+        <v>6964571</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9058,12 +8411,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9078,27 +8431,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>120722075</v>
+        <v>109838389</v>
       </c>
       <c r="B81" t="n">
-        <v>91952</v>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9106,34 +8454,34 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4362</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>550613</v>
+        <v>550495</v>
       </c>
       <c r="R81" t="n">
-        <v>6964642</v>
+        <v>6964512</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9160,12 +8508,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9180,62 +8528,57 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>120721987</v>
+        <v>109838393</v>
       </c>
       <c r="B82" t="n">
-        <v>90176</v>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>2051</v>
+        <v>228912</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>550628</v>
+        <v>550450</v>
       </c>
       <c r="R82" t="n">
-        <v>6964480</v>
+        <v>6964486</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9262,12 +8605,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9282,62 +8625,57 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erica Hästdahl</t>
+          <t>Edith Bremer Storm</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>120722010</v>
+        <v>109838394</v>
       </c>
       <c r="B83" t="n">
-        <v>89365</v>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6276</v>
+        <v>228912</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Getingsfors, Jmt</t>
+          <t>Getingfors, Jmt</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>550507</v>
+        <v>550479</v>
       </c>
       <c r="R83" t="n">
-        <v>6964571</v>
+        <v>6964446</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9364,12 +8702,12 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2024-09-10</t>
+          <t>2023-05-21</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9384,15 +8722,698 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>109838397</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Getingfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>550504</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6964453</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2023-05-21</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2023-05-21</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>109838470</v>
+      </c>
+      <c r="B85" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Getingfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>550538</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6964600</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>109729421</v>
+      </c>
+      <c r="B86" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Getingfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>550640</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6964470</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2023-05-19</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Rasmus Viding</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>109838391</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Getingfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>550450</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6964486</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2023-05-21</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2023-05-21</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>109838398</v>
+      </c>
+      <c r="B88" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Getingfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>550504</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6964453</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2023-05-21</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2023-05-21</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Edith Bremer Storm</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>113232832</v>
+      </c>
+      <c r="B89" t="n">
+        <v>91402</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>256703</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Tallfingersvamp</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Ramaria eosanguinea</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Väster om Gimån vid Nyängesselet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>550412</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6964365</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2023-08-28</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Johan Staaf</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Pontus Wallén</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr">
+        <is>
+          <t>LstZ inventering av skogliga värdetrakter 2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>120722012</v>
+      </c>
+      <c r="B90" t="n">
+        <v>91431</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>6039941</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Gelatinfingersvamp</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Ramaria primulina</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Getingsfors, Jmt</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>550640</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6964488</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Hällesjö</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2024-09-10</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
           <t>Erica Hästdahl</t>
         </is>
       </c>
-      <c r="AX83" t="inlineStr">
+      <c r="AX90" t="inlineStr">
         <is>
           <t>Erica Hästdahl</t>
         </is>
       </c>
-      <c r="AY83" t="inlineStr"/>
+      <c r="AY90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AZ90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109729419</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838387</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838390</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838396</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1161,6 +1186,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232562</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838401</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109729407</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1558,6 +1603,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721987</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1673,6 +1723,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790348</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96790349</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232793</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232795</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2091,6 +2161,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232798</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2192,6 +2267,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232800</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2293,6 +2373,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232804</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2394,6 +2479,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232825</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2491,6 +2581,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721966</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2588,6 +2683,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721967</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2685,6 +2785,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721968</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2782,6 +2887,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721969</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2883,6 +2993,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232513</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2980,6 +3095,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721947</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3077,6 +3197,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721933</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3174,6 +3299,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721934</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3271,6 +3401,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721935</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3368,6 +3503,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721936</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3465,6 +3605,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721937</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3562,6 +3707,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721938</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3659,6 +3809,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721991</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3756,6 +3911,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721993</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3857,6 +4017,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232836</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -3958,6 +4123,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232837</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4055,6 +4225,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722062</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4152,6 +4327,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722063</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4249,6 +4429,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722064</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4346,6 +4531,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722065</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4443,6 +4633,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722066</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4540,6 +4735,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722068</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4637,6 +4837,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722069</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4734,6 +4939,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722070</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4831,6 +5041,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722071</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -4928,6 +5143,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722072</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5025,6 +5245,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722075</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5122,6 +5347,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722076</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5219,6 +5449,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722077</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5316,6 +5551,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109729412</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5413,6 +5653,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722016</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5510,6 +5755,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722019</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5611,6 +5861,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232531</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5712,6 +5967,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232794</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -5813,6 +6073,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232831</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -5910,6 +6175,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721971</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6007,6 +6277,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721972</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6104,6 +6379,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721973</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6201,6 +6481,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721948</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6298,6 +6583,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721949</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6395,6 +6685,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721951</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6496,6 +6791,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232489</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6597,6 +6897,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232811</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -6694,6 +6999,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722010</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -6791,6 +7101,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722011</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -6888,6 +7203,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120721943</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -6985,6 +7305,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838400</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7082,6 +7407,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838392</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7179,6 +7509,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838402</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7276,6 +7611,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838386</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7373,6 +7713,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109729411</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7470,6 +7815,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109729420</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -7567,6 +7917,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838381</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -7664,6 +8019,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838382</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -7761,6 +8121,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838384</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -7858,6 +8223,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838388</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -7955,6 +8325,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838395</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8052,6 +8427,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838399</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8149,6 +8529,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109729422</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8246,6 +8631,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838380</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8343,6 +8733,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838383</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8440,6 +8835,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838385</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -8537,6 +8937,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838389</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -8634,6 +9039,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838393</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -8731,6 +9141,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838394</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -8828,6 +9243,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838397</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -8925,6 +9345,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838470</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9022,6 +9447,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109729421</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9119,6 +9549,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838391</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9216,6 +9651,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109838398</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9317,6 +9757,11 @@
           <t>LstZ inventering av skogliga värdetrakter 2023</t>
         </is>
       </c>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113232832</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9414,8 +9859,104 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120722012</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -1512,7 +1512,7 @@
         <v>120721987</v>
       </c>
       <c r="B10" t="n">
-        <v>91394</v>
+        <v>91533</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -1512,7 +1512,7 @@
         <v>120721987</v>
       </c>
       <c r="B10" t="n">
-        <v>91533</v>
+        <v>91535</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -1512,7 +1512,7 @@
         <v>120721987</v>
       </c>
       <c r="B10" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -1512,7 +1512,7 @@
         <v>120721987</v>
       </c>
       <c r="B10" t="n">
-        <v>91536</v>
+        <v>91537</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -1512,7 +1512,7 @@
         <v>120721987</v>
       </c>
       <c r="B10" t="n">
-        <v>91537</v>
+        <v>91538</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -1512,7 +1512,7 @@
         <v>120721987</v>
       </c>
       <c r="B10" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 31557-2024 artfynd.xlsx
+++ b/artfynd/A 31557-2024 artfynd.xlsx
@@ -1512,7 +1512,7 @@
         <v>120721987</v>
       </c>
       <c r="B10" t="n">
-        <v>91544</v>
+        <v>91545</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
